--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="O20" t="n">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4554286656204539</v>
+        <v>0.9292213903385069</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="O21" t="n">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1289</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O12" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8116914121138735</v>
+        <v>0.8080186002943539</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O13" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O20" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9292213903385069</v>
+        <v>0.9365670139775465</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O21" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="O20" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9365670139775465</v>
+        <v>0.9549310730751454</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="O21" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1419</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O20" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9549310730751454</v>
+        <v>0.9512582612556257</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O21" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8080186002943539</v>
+        <v>0.8263826593919528</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="O13" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O20" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9512582612556257</v>
+        <v>0.980640755811784</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="O21" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1423</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8263826593919528</v>
+        <v>0.8190370357529132</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="O13" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O20" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="R20" t="n">
-        <v>0.980640755811784</v>
+        <v>0.9879863794508235</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O21" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O20" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9879863794508235</v>
+        <v>0.9916591912703433</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O21" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O20" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9916591912703433</v>
+        <v>0.9953320030898631</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O21" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8190370357529132</v>
+        <v>0.8263826593919528</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O13" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O20" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9953320030898631</v>
+        <v>1.002677626728903</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O21" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="O29" t="n">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1028387309465541</v>
+        <v>0.7786361057381954</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="O30" t="n">
-        <v>28</v>
+        <v>212</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1438</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O29" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7786361057381954</v>
+        <v>0.7859817293772351</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O30" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -21367,13 +21367,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O109" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R109" t="n">
-        <v>1.002677626728903</v>
+        <v>0.9990048149093829</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O110" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -24661,13 +24661,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O126" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="R126" t="n">
-        <v>0.7970001648357945</v>
+        <v>0.7896545411967548</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O127" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3130</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -21367,13 +21367,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O109" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R109" t="n">
-        <v>0.9990048149093829</v>
+        <v>1.002677626728903</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O110" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -21367,13 +21367,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O109" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R109" t="n">
-        <v>1.002677626728903</v>
+        <v>1.006350438548423</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O110" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -24661,13 +24661,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="O126" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="R126" t="n">
-        <v>0.7896545411967548</v>
+        <v>0.8153642239333934</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="O127" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3128</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21215,7 +21215,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21367,13 +21367,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O109" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R109" t="n">
-        <v>1.006350438548423</v>
+        <v>1.002677626728903</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O110" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22394,7 +22394,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22787,7 +22787,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23573,7 +23573,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24661,13 +24661,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O126" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R126" t="n">
-        <v>0.8153642239333934</v>
+        <v>0.8116914121138735</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -24820,10 +24820,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O127" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25295,7 +25295,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25688,7 +25688,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26624,7 +26624,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -28066,7 +28066,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3136</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -9031,13 +9031,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O60" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R60" t="n">
-        <v>1.002677626728903</v>
+        <v>1.006350438548423</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="O69" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="R69" t="n">
-        <v>0.8043457884748341</v>
+        <v>0.8337282830309923</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3132</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -9031,13 +9031,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O60" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R60" t="n">
-        <v>1.006350438548423</v>
+        <v>1.002677626728903</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O69" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R69" t="n">
-        <v>0.8337282830309923</v>
+        <v>0.8374010948505122</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -9031,13 +9031,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O60" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="R60" t="n">
-        <v>1.002677626728903</v>
+        <v>1.006350438548423</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3141</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O69" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R69" t="n">
-        <v>0.8374010948505122</v>
+        <v>0.841073906670032</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11533,6 +11533,150 @@
         </is>
       </c>
       <c r="BC77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>syphilis-over-two-years-or-unspecified-duration</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D233</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Syphilis over two years or unspecified duration</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>病程超过两年或病程未明的梅毒</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>163</v>
+      </c>
+      <c r="O78" t="n">
+        <v>163</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.5986683265817258</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_GT2Y_OR_UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -11571,7 +11715,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11798,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -11664,7 +11808,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -11716,7 +11860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3142</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d233/2026-2029.xlsx
+++ b/diseases/d233/2026-2029.xlsx
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O69" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R69" t="n">
-        <v>0.841073906670032</v>
+        <v>0.8484195303090715</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3306</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="16">
